--- a/projetos/gestao-ia-planilhas/produto/kit-completo/02-relatorio-mensal-pronto.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/02-relatorio-mensal-pronto.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>A Prisma Comunicação é uma empresa fictícia. Os números são inventados. Apague-os antes de começar.</t>
+          <t>A Prisma Comunicação é uma empresa fictícia. Os números são inventados. Apague-os antes de começar. A planilha Ganhos e Gastos do kit usa outro exemplo, de uma autônoma, porque ela serve também para o dinheiro pessoal — não é descuido, é o uso previsto.</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="H11" s="9">
         <f>IF(Indicadores!A11="","",Indicadores!R11)</f>
-        <v>80700</v>
+        <v>8966.66666666667</v>
       </c>
       <c r="I11" s="11" t="str">
         <f>IF(Indicadores!A11="","",Indicadores!B11)</f>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="H16" s="9">
         <f>IF(Indicadores!A16="","",Indicadores!R16)</f>
-        <v>405.8</v>
+        <v>45.0888888888889</v>
       </c>
       <c r="I16" s="11" t="str">
         <f>IF(Indicadores!A16="","",Indicadores!B16)</f>
@@ -1570,9 +1570,10 @@
           <t>Indicador do gráfico</t>
         </is>
       </c>
-      <c r="B18" s="14" t="str">
-        <f>Indicadores!A5</f>
-        <v>Receita</v>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
       </c>
       <c r="C18" s="15" t="n"/>
       <c r="D18" s="16" t="n"/>
@@ -1792,7 +1793,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>=OFFSET(Indicadores!$A$5,0,0,MAX(1,COUNTA(Indicadores!$A$5:$A$16)),1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -1929,7 +1930,7 @@
     </row>
     <row r="22">
       <c r="A22" s="19" t="str">
-        <f>IF(COUNT(Painel!$O$5:$O$16)=0,"• Nenhum indicador fora da meta.",IFERROR("• Mais longe da meta: "&amp;INDEX(Painel!$A$5:$A$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&amp;" ("&amp;IF(INDEX(Painel!$F$5:$F$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&gt;=0,"+","")&amp;FIXED(INDEX(Painel!$F$5:$F$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))*100,0)&amp;"% da meta, "&amp;LOWER(INDEX(Painel!$G$5:$G$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0)))&amp;").",""))</f>
+        <f>IF((COUNTIF(Painel!$G$5:$G$16,"Acima da meta")+COUNTIF(Painel!$G$5:$G$16,"Abaixo da meta"))=0,"• Nenhum indicador fora da meta.",IF(COUNT(Painel!$O$5:$O$16)=0,"• "&amp;(COUNTIF(Painel!$G$5:$G$16,"Acima da meta")+COUNTIF(Painel!$G$5:$G$16,"Abaixo da meta"))&amp;" indicador(es) fora da meta (sem percentual: a meta é zero).",IFERROR("• Mais longe da meta: "&amp;INDEX(Painel!$A$5:$A$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&amp;" ("&amp;IF(INDEX(Painel!$F$5:$F$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))&gt;=0,"+","")&amp;FIXED(INDEX(Painel!$F$5:$F$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0))*100,0)&amp;"% da meta, "&amp;LOWER(INDEX(Painel!$G$5:$G$16,MATCH(MAX(Painel!$O$5:$O$16),Painel!$O$5:$O$16,0)))&amp;").","")))</f>
         <v>• Mais longe da meta: Taxa de conversão de leads (-12% da meta, abaixo da meta).</v>
       </c>
     </row>
@@ -2176,7 +2177,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <dataValidations count="1">
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>=Config!$D$5:$D$16</formula1>
     </dataValidation>
   </dataValidations>
@@ -2190,7 +2191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2316,12 +2317,17 @@
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>Acumulado (soma; média para % e pts)</t>
+          <t>Acumulado</t>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
           <t>Média</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
+        <is>
+          <t>Como acumular</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2384,17 @@
       <c r="P5" s="23" t="n"/>
       <c r="Q5" s="23" t="n"/>
       <c r="R5" s="9">
-        <f>IF(COUNT(F5:Q5)=0,"",IF(OR(B5="%",B5="pts"),AVERAGE(F5:Q5),SUM(F5:Q5)))</f>
+        <f>IF(COUNT(F5:Q5)=0,"",IF(T5="Média",AVERAGE(F5:Q5),SUM(F5:Q5)))</f>
         <v>1033600</v>
       </c>
       <c r="S5" s="9">
         <f>IF(COUNT(F5:Q5)=0,"",AVERAGE(F5:Q5))</f>
         <v>114844.444444444</v>
+      </c>
+      <c r="T5" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2439,12 +2450,17 @@
       <c r="P6" s="23" t="n"/>
       <c r="Q6" s="23" t="n"/>
       <c r="R6" s="9">
-        <f>IF(COUNT(F6:Q6)=0,"",IF(OR(B6="%",B6="pts"),AVERAGE(F6:Q6),SUM(F6:Q6)))</f>
+        <f>IF(COUNT(F6:Q6)=0,"",IF(T6="Média",AVERAGE(F6:Q6),SUM(F6:Q6)))</f>
         <v>766600</v>
       </c>
       <c r="S6" s="9">
         <f>IF(COUNT(F6:Q6)=0,"",AVERAGE(F6:Q6))</f>
         <v>85177.7777777778</v>
+      </c>
+      <c r="T6" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -2500,12 +2516,17 @@
       <c r="P7" s="23" t="n"/>
       <c r="Q7" s="23" t="n"/>
       <c r="R7" s="9">
-        <f>IF(COUNT(F7:Q7)=0,"",IF(OR(B7="%",B7="pts"),AVERAGE(F7:Q7),SUM(F7:Q7)))</f>
+        <f>IF(COUNT(F7:Q7)=0,"",IF(T7="Média",AVERAGE(F7:Q7),SUM(F7:Q7)))</f>
         <v>267000</v>
       </c>
       <c r="S7" s="9">
         <f>IF(COUNT(F7:Q7)=0,"",AVERAGE(F7:Q7))</f>
         <v>29666.6666666667</v>
+      </c>
+      <c r="T7" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2561,12 +2582,17 @@
       <c r="P8" s="23" t="n"/>
       <c r="Q8" s="23" t="n"/>
       <c r="R8" s="9">
-        <f>IF(COUNT(F8:Q8)=0,"",IF(OR(B8="%",B8="pts"),AVERAGE(F8:Q8),SUM(F8:Q8)))</f>
+        <f>IF(COUNT(F8:Q8)=0,"",IF(T8="Média",AVERAGE(F8:Q8),SUM(F8:Q8)))</f>
         <v>44</v>
       </c>
       <c r="S8" s="9">
         <f>IF(COUNT(F8:Q8)=0,"",AVERAGE(F8:Q8))</f>
         <v>4.88888888888889</v>
+      </c>
+      <c r="T8" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2622,12 +2648,17 @@
       <c r="P9" s="23" t="n"/>
       <c r="Q9" s="23" t="n"/>
       <c r="R9" s="9">
-        <f>IF(COUNT(F9:Q9)=0,"",IF(OR(B9="%",B9="pts"),AVERAGE(F9:Q9),SUM(F9:Q9)))</f>
+        <f>IF(COUNT(F9:Q9)=0,"",IF(T9="Média",AVERAGE(F9:Q9),SUM(F9:Q9)))</f>
         <v>1032</v>
       </c>
       <c r="S9" s="9">
         <f>IF(COUNT(F9:Q9)=0,"",AVERAGE(F9:Q9))</f>
         <v>114.666666666667</v>
+      </c>
+      <c r="T9" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -2683,12 +2714,17 @@
       <c r="P10" s="23" t="n"/>
       <c r="Q10" s="23" t="n"/>
       <c r="R10" s="9">
-        <f>IF(COUNT(F10:Q10)=0,"",IF(OR(B10="%",B10="pts"),AVERAGE(F10:Q10),SUM(F10:Q10)))</f>
+        <f>IF(COUNT(F10:Q10)=0,"",IF(T10="Média",AVERAGE(F10:Q10),SUM(F10:Q10)))</f>
         <v>4.2</v>
       </c>
       <c r="S10" s="9">
         <f>IF(COUNT(F10:Q10)=0,"",AVERAGE(F10:Q10))</f>
         <v>4.2</v>
+      </c>
+      <c r="T10" s="14" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -2744,12 +2780,17 @@
       <c r="P11" s="23" t="n"/>
       <c r="Q11" s="23" t="n"/>
       <c r="R11" s="9">
-        <f>IF(COUNT(F11:Q11)=0,"",IF(OR(B11="%",B11="pts"),AVERAGE(F11:Q11),SUM(F11:Q11)))</f>
-        <v>80700</v>
+        <f>IF(COUNT(F11:Q11)=0,"",IF(T11="Média",AVERAGE(F11:Q11),SUM(F11:Q11)))</f>
+        <v>8966.66666666667</v>
       </c>
       <c r="S11" s="9">
         <f>IF(COUNT(F11:Q11)=0,"",AVERAGE(F11:Q11))</f>
         <v>8966.66666666667</v>
+      </c>
+      <c r="T11" s="14" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -2805,12 +2846,17 @@
       <c r="P12" s="23" t="n"/>
       <c r="Q12" s="23" t="n"/>
       <c r="R12" s="9">
-        <f>IF(COUNT(F12:Q12)=0,"",IF(OR(B12="%",B12="pts"),AVERAGE(F12:Q12),SUM(F12:Q12)))</f>
+        <f>IF(COUNT(F12:Q12)=0,"",IF(T12="Média",AVERAGE(F12:Q12),SUM(F12:Q12)))</f>
         <v>3.22222222222222</v>
       </c>
       <c r="S12" s="9">
         <f>IF(COUNT(F12:Q12)=0,"",AVERAGE(F12:Q12))</f>
         <v>3.22222222222222</v>
+      </c>
+      <c r="T12" s="14" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -2866,12 +2912,17 @@
       <c r="P13" s="23" t="n"/>
       <c r="Q13" s="23" t="n"/>
       <c r="R13" s="9">
-        <f>IF(COUNT(F13:Q13)=0,"",IF(OR(B13="%",B13="pts"),AVERAGE(F13:Q13),SUM(F13:Q13)))</f>
+        <f>IF(COUNT(F13:Q13)=0,"",IF(T13="Média",AVERAGE(F13:Q13),SUM(F13:Q13)))</f>
         <v>536</v>
       </c>
       <c r="S13" s="9">
         <f>IF(COUNT(F13:Q13)=0,"",AVERAGE(F13:Q13))</f>
         <v>59.5555555555556</v>
+      </c>
+      <c r="T13" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -2927,12 +2978,17 @@
       <c r="P14" s="23" t="n"/>
       <c r="Q14" s="23" t="n"/>
       <c r="R14" s="9">
-        <f>IF(COUNT(F14:Q14)=0,"",IF(OR(B14="%",B14="pts"),AVERAGE(F14:Q14),SUM(F14:Q14)))</f>
+        <f>IF(COUNT(F14:Q14)=0,"",IF(T14="Média",AVERAGE(F14:Q14),SUM(F14:Q14)))</f>
         <v>68.8888888888889</v>
       </c>
       <c r="S14" s="9">
         <f>IF(COUNT(F14:Q14)=0,"",AVERAGE(F14:Q14))</f>
         <v>68.8888888888889</v>
+      </c>
+      <c r="T14" s="14" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -2988,12 +3044,17 @@
       <c r="P15" s="23" t="n"/>
       <c r="Q15" s="23" t="n"/>
       <c r="R15" s="9">
-        <f>IF(COUNT(F15:Q15)=0,"",IF(OR(B15="%",B15="pts"),AVERAGE(F15:Q15),SUM(F15:Q15)))</f>
+        <f>IF(COUNT(F15:Q15)=0,"",IF(T15="Média",AVERAGE(F15:Q15),SUM(F15:Q15)))</f>
         <v>173</v>
       </c>
       <c r="S15" s="9">
         <f>IF(COUNT(F15:Q15)=0,"",AVERAGE(F15:Q15))</f>
         <v>19.2222222222222</v>
+      </c>
+      <c r="T15" s="14" t="inlineStr">
+        <is>
+          <t>Soma</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -3049,36 +3110,44 @@
       <c r="P16" s="23" t="n"/>
       <c r="Q16" s="23" t="n"/>
       <c r="R16" s="9">
-        <f>IF(COUNT(F16:Q16)=0,"",IF(OR(B16="%",B16="pts"),AVERAGE(F16:Q16),SUM(F16:Q16)))</f>
-        <v>405.8</v>
+        <f>IF(COUNT(F16:Q16)=0,"",IF(T16="Média",AVERAGE(F16:Q16),SUM(F16:Q16)))</f>
+        <v>45.0888888888889</v>
       </c>
       <c r="S16" s="9">
         <f>IF(COUNT(F16:Q16)=0,"",AVERAGE(F16:Q16))</f>
         <v>45.0888888888889</v>
       </c>
+      <c r="T16" s="14" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>"Acumulado" soma os meses preenchidos quando a unidade é R$, un ou h; quando é % ou pts (taxas, notas), mostra a média dos meses, porque somar taxas não faz sentido. "Média" é sempre a média. Para indicadores em %, digite 4,5 (não 0,045).</t>
+          <t>"Como acumular" decide o que o Acumulado mostra: Soma para o que se empilha (receita, despesa, quantidade, horas) e Média para razão (ticket médio, custo por lead, taxa, nota). Somar razão não significa nada: doze meses de ticket médio somados não são o ticket do ano. "Média" é sempre a média dos meses preenchidos. Para indicadores em %, digite 4,5 (não 0,045).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="2">
-    <mergeCell ref="A18:S18"/>
+    <mergeCell ref="A18:T18"/>
     <mergeCell ref="A2:R2"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="E5:E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="E5:E16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5:B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5:B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"R$,%,un,h,pts"</formula1>
+    </dataValidation>
+    <dataValidation sqref="T5:T16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Como acumular" error="Escolha Soma (empilha) ou Média (razão)." type="list">
+      <formula1>"Soma,Média"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/02-relatorio-mensal-pronto.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/02-relatorio-mensal-pronto.xlsx
@@ -767,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -796,125 +796,137 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Você digita até 12 indicadores por mês; ela calcula variação contra o mês anterior, comparação com a meta, acumulado (soma; média para % e pts) e média, monta o painel e escreve as frases-base do relatório para você colar na IA.</t>
+          <t>Você digita até 12 indicadores por mês; ela calcula variação contra o mês anterior, comparação com a meta, acumulado, média, monta o painel e escreve as frases-base do relatório para você colar na IA.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Passo 1</t>
+          <t>Como acumular</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Em Config, preencha o nome da empresa ou área, o ano e escolha o mês do relatório.</t>
+          <t>Cada indicador tem a sua regra, escolhida na última coluna da aba Indicadores: "Soma" para o que se empilha (receita, despesa, quantidade, horas) e "Média" para razão (ticket médio, custo por lead, taxa de conversão, inadimplência, NPS) — inclusive quando a razão está em reais. Somar razão não significa nada: doze meses de ticket médio somados não são o ticket do ano. A Média usa só os meses preenchidos; um mês com zero digitado ENTRA na conta, um mês em branco não.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Passo 2</t>
+          <t>Passo 1</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Em Indicadores, troque os exemplos pelos seus (de cima para baixo, sem pular linha): nome, unidade (R$, %, un, h, pts), casas decimais, meta mensal e se maior é melhor. Depois, o valor de cada mês. Em %, digite 4,5 e não 0,045.</t>
+          <t>Em Config, preencha o nome da empresa ou área, o ano e escolha o mês do relatório.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Passo 3</t>
+          <t>Passo 2</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Abra Painel: cada indicador com mês, mês anterior, variação, meta e situação (verde no alvo, vermelho fora). Escolha um indicador para o gráfico de evolução.</t>
+          <t>Em Indicadores, troque os exemplos pelos seus (de cima para baixo, sem pular linha): nome, unidade (R$, %, un, h, pts), casas decimais, meta mensal e se maior é melhor. Depois, o valor de cada mês. Em %, digite 4,5 e não 0,045.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Passo 4</t>
+          <t>Passo 3</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Abra Resumo: as frases do mês já estão escritas. Copie o bloco único e cole no prompt "Escrever 01" (relatório executivo) ou "Apresentar 01" (roteiro de 8 slides) da biblioteca do kit, junto com os seus comentários sobre o porquê dos números.</t>
+          <t>Abra Painel: cada indicador com mês, mês anterior, variação, meta e situação (verde no alvo, vermelho fora). Escolha um indicador para o gráfico de evolução.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Todo mês</t>
+          <t>Passo 4</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Digite os valores do novo mês em Indicadores e troque o mês em Config. O resto se refaz sozinho.</t>
+          <t>Abra Resumo: as frases do mês já estão escritas. Copie o bloco único e cole no prompt "Escrever 01" (relatório executivo) ou "Apresentar 01" (roteiro de 8 slides) da biblioteca do kit, junto com os seus comentários sobre o porquê dos números.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Legenda</t>
+          <t>Todo mês</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Células amarelas: você preenche. Células brancas: calculadas. Verde: no alvo. Vermelho: fora da meta.</t>
+          <t>Digite os valores do novo mês em Indicadores e troque o mês em Config. O resto se refaz sozinho.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Proteção</t>
+          <t>Legenda</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
+          <t>Células amarelas: você preenche. Células brancas: calculadas. Verde: no alvo. Vermelho: fora da meta.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Proteção</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráfico funcionam.</t>
+          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>A Prisma Comunicação é uma empresa fictícia. Os números são inventados. Apague-os antes de começar. A planilha Ganhos e Gastos do kit usa outro exemplo, de uma autônoma, porque ela serve também para o dinheiro pessoal — não é descuido, é o uso previsto.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráfico funcionam.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>A Prisma Comunicação é uma empresa fictícia. Os números são inventados. Apague-os antes de começar. A planilha Ganhos e Gastos do kit usa outro exemplo, de uma autônoma, porque ela serve também para o dinheiro pessoal — não é descuido, é o uso previsto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1839,73 +1851,73 @@
     </row>
     <row r="6">
       <c r="A6" s="19" t="str">
-        <f>IF(OR(Indicadores!A5="",Painel!B5=""),"","• "&amp;Indicadores!A5&amp;": "&amp;IF(Indicadores!B5="R$","R$ ","")&amp;FIXED(Painel!B5,IF(Indicadores!C5="",0,Indicadores!C5))&amp;IF(OR(Indicadores!B5="R$",Indicadores!B5=""),""," "&amp;Indicadores!B5)&amp;IF(Painel!C5&lt;&gt;"",IF(Painel!D5&gt;=0," (+"," (")&amp;FIXED(Painel!D5*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E5&lt;&gt;"","; meta "&amp;IF(Indicadores!B5="R$","R$ ","")&amp;FIXED(Painel!E5,IF(Indicadores!C5="",0,Indicadores!C5))&amp;IF(OR(Indicadores!B5="R$",Indicadores!B5=""),""," "&amp;Indicadores!B5)&amp;", "&amp;LOWER(Painel!G5),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A5="",Painel!B5=""),"","• "&amp;Indicadores!A5&amp;": "&amp;IF(Indicadores!B5="R$","R$ ","")&amp;FIXED(Painel!B5,IF(Indicadores!C5="",0,Indicadores!C5))&amp;IF(OR(Indicadores!B5="R$",Indicadores!B5=""),""," "&amp;Indicadores!B5)&amp;IF(Painel!C5="","",IF(AND(Painel!C5=0,Painel!B5&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D5="","",IF(Painel!D5&gt;=0," (+"," (")&amp;FIXED(Painel!D5*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E5&lt;&gt;"","; meta "&amp;IF(Indicadores!B5="R$","R$ ","")&amp;FIXED(Painel!E5,IF(Indicadores!C5="",0,Indicadores!C5))&amp;IF(OR(Indicadores!B5="R$",Indicadores!B5=""),""," "&amp;Indicadores!B5)&amp;", "&amp;LOWER(Painel!G5),"")&amp;".")</f>
         <v>• Receita: R$ 131.200 (+5% em relação a Agosto); meta R$ 120.000, no alvo.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="str">
-        <f>IF(OR(Indicadores!A6="",Painel!B6=""),"","• "&amp;Indicadores!A6&amp;": "&amp;IF(Indicadores!B6="R$","R$ ","")&amp;FIXED(Painel!B6,IF(Indicadores!C6="",0,Indicadores!C6))&amp;IF(OR(Indicadores!B6="R$",Indicadores!B6=""),""," "&amp;Indicadores!B6)&amp;IF(Painel!C6&lt;&gt;"",IF(Painel!D6&gt;=0," (+"," (")&amp;FIXED(Painel!D6*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E6&lt;&gt;"","; meta "&amp;IF(Indicadores!B6="R$","R$ ","")&amp;FIXED(Painel!E6,IF(Indicadores!C6="",0,Indicadores!C6))&amp;IF(OR(Indicadores!B6="R$",Indicadores!B6=""),""," "&amp;Indicadores!B6)&amp;", "&amp;LOWER(Painel!G6),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A6="",Painel!B6=""),"","• "&amp;Indicadores!A6&amp;": "&amp;IF(Indicadores!B6="R$","R$ ","")&amp;FIXED(Painel!B6,IF(Indicadores!C6="",0,Indicadores!C6))&amp;IF(OR(Indicadores!B6="R$",Indicadores!B6=""),""," "&amp;Indicadores!B6)&amp;IF(Painel!C6="","",IF(AND(Painel!C6=0,Painel!B6&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D6="","",IF(Painel!D6&gt;=0," (+"," (")&amp;FIXED(Painel!D6*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E6&lt;&gt;"","; meta "&amp;IF(Indicadores!B6="R$","R$ ","")&amp;FIXED(Painel!E6,IF(Indicadores!C6="",0,Indicadores!C6))&amp;IF(OR(Indicadores!B6="R$",Indicadores!B6=""),""," "&amp;Indicadores!B6)&amp;", "&amp;LOWER(Painel!G6),"")&amp;".")</f>
         <v>• Despesas: R$ 89.800 (+3% em relação a Agosto); meta R$ 85.000, acima da meta.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="str">
-        <f>IF(OR(Indicadores!A7="",Painel!B7=""),"","• "&amp;Indicadores!A7&amp;": "&amp;IF(Indicadores!B7="R$","R$ ","")&amp;FIXED(Painel!B7,IF(Indicadores!C7="",0,Indicadores!C7))&amp;IF(OR(Indicadores!B7="R$",Indicadores!B7=""),""," "&amp;Indicadores!B7)&amp;IF(Painel!C7&lt;&gt;"",IF(Painel!D7&gt;=0," (+"," (")&amp;FIXED(Painel!D7*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E7&lt;&gt;"","; meta "&amp;IF(Indicadores!B7="R$","R$ ","")&amp;FIXED(Painel!E7,IF(Indicadores!C7="",0,Indicadores!C7))&amp;IF(OR(Indicadores!B7="R$",Indicadores!B7=""),""," "&amp;Indicadores!B7)&amp;", "&amp;LOWER(Painel!G7),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A7="",Painel!B7=""),"","• "&amp;Indicadores!A7&amp;": "&amp;IF(Indicadores!B7="R$","R$ ","")&amp;FIXED(Painel!B7,IF(Indicadores!C7="",0,Indicadores!C7))&amp;IF(OR(Indicadores!B7="R$",Indicadores!B7=""),""," "&amp;Indicadores!B7)&amp;IF(Painel!C7="","",IF(AND(Painel!C7=0,Painel!B7&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D7="","",IF(Painel!D7&gt;=0," (+"," (")&amp;FIXED(Painel!D7*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E7&lt;&gt;"","; meta "&amp;IF(Indicadores!B7="R$","R$ ","")&amp;FIXED(Painel!E7,IF(Indicadores!C7="",0,Indicadores!C7))&amp;IF(OR(Indicadores!B7="R$",Indicadores!B7=""),""," "&amp;Indicadores!B7)&amp;", "&amp;LOWER(Painel!G7),"")&amp;".")</f>
         <v>• Resultado (receita - despesas): R$ 41.400 (+11% em relação a Agosto); meta R$ 35.000, no alvo.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="str">
-        <f>IF(OR(Indicadores!A8="",Painel!B8=""),"","• "&amp;Indicadores!A8&amp;": "&amp;IF(Indicadores!B8="R$","R$ ","")&amp;FIXED(Painel!B8,IF(Indicadores!C8="",0,Indicadores!C8))&amp;IF(OR(Indicadores!B8="R$",Indicadores!B8=""),""," "&amp;Indicadores!B8)&amp;IF(Painel!C8&lt;&gt;"",IF(Painel!D8&gt;=0," (+"," (")&amp;FIXED(Painel!D8*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E8&lt;&gt;"","; meta "&amp;IF(Indicadores!B8="R$","R$ ","")&amp;FIXED(Painel!E8,IF(Indicadores!C8="",0,Indicadores!C8))&amp;IF(OR(Indicadores!B8="R$",Indicadores!B8=""),""," "&amp;Indicadores!B8)&amp;", "&amp;LOWER(Painel!G8),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A8="",Painel!B8=""),"","• "&amp;Indicadores!A8&amp;": "&amp;IF(Indicadores!B8="R$","R$ ","")&amp;FIXED(Painel!B8,IF(Indicadores!C8="",0,Indicadores!C8))&amp;IF(OR(Indicadores!B8="R$",Indicadores!B8=""),""," "&amp;Indicadores!B8)&amp;IF(Painel!C8="","",IF(AND(Painel!C8=0,Painel!B8&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D8="","",IF(Painel!D8&gt;=0," (+"," (")&amp;FIXED(Painel!D8*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E8&lt;&gt;"","; meta "&amp;IF(Indicadores!B8="R$","R$ ","")&amp;FIXED(Painel!E8,IF(Indicadores!C8="",0,Indicadores!C8))&amp;IF(OR(Indicadores!B8="R$",Indicadores!B8=""),""," "&amp;Indicadores!B8)&amp;", "&amp;LOWER(Painel!G8),"")&amp;".")</f>
         <v>• Novos clientes: 6 un (-14% em relação a Agosto); meta 6 un, no alvo.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="str">
-        <f>IF(OR(Indicadores!A9="",Painel!B9=""),"","• "&amp;Indicadores!A9&amp;": "&amp;IF(Indicadores!B9="R$","R$ ","")&amp;FIXED(Painel!B9,IF(Indicadores!C9="",0,Indicadores!C9))&amp;IF(OR(Indicadores!B9="R$",Indicadores!B9=""),""," "&amp;Indicadores!B9)&amp;IF(Painel!C9&lt;&gt;"",IF(Painel!D9&gt;=0," (+"," (")&amp;FIXED(Painel!D9*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E9&lt;&gt;"","; meta "&amp;IF(Indicadores!B9="R$","R$ ","")&amp;FIXED(Painel!E9,IF(Indicadores!C9="",0,Indicadores!C9))&amp;IF(OR(Indicadores!B9="R$",Indicadores!B9=""),""," "&amp;Indicadores!B9)&amp;", "&amp;LOWER(Painel!G9),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A9="",Painel!B9=""),"","• "&amp;Indicadores!A9&amp;": "&amp;IF(Indicadores!B9="R$","R$ ","")&amp;FIXED(Painel!B9,IF(Indicadores!C9="",0,Indicadores!C9))&amp;IF(OR(Indicadores!B9="R$",Indicadores!B9=""),""," "&amp;Indicadores!B9)&amp;IF(Painel!C9="","",IF(AND(Painel!C9=0,Painel!B9&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D9="","",IF(Painel!D9&gt;=0," (+"," (")&amp;FIXED(Painel!D9*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E9&lt;&gt;"","; meta "&amp;IF(Indicadores!B9="R$","R$ ","")&amp;FIXED(Painel!E9,IF(Indicadores!C9="",0,Indicadores!C9))&amp;IF(OR(Indicadores!B9="R$",Indicadores!B9=""),""," "&amp;Indicadores!B9)&amp;", "&amp;LOWER(Painel!G9),"")&amp;".")</f>
         <v>• Leads recebidos: 137 un (-4% em relação a Agosto); meta 120 un, no alvo.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="str">
-        <f>IF(OR(Indicadores!A10="",Painel!B10=""),"","• "&amp;Indicadores!A10&amp;": "&amp;IF(Indicadores!B10="R$","R$ ","")&amp;FIXED(Painel!B10,IF(Indicadores!C10="",0,Indicadores!C10))&amp;IF(OR(Indicadores!B10="R$",Indicadores!B10=""),""," "&amp;Indicadores!B10)&amp;IF(Painel!C10&lt;&gt;"",IF(Painel!D10&gt;=0," (+"," (")&amp;FIXED(Painel!D10*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E10&lt;&gt;"","; meta "&amp;IF(Indicadores!B10="R$","R$ ","")&amp;FIXED(Painel!E10,IF(Indicadores!C10="",0,Indicadores!C10))&amp;IF(OR(Indicadores!B10="R$",Indicadores!B10=""),""," "&amp;Indicadores!B10)&amp;", "&amp;LOWER(Painel!G10),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A10="",Painel!B10=""),"","• "&amp;Indicadores!A10&amp;": "&amp;IF(Indicadores!B10="R$","R$ ","")&amp;FIXED(Painel!B10,IF(Indicadores!C10="",0,Indicadores!C10))&amp;IF(OR(Indicadores!B10="R$",Indicadores!B10=""),""," "&amp;Indicadores!B10)&amp;IF(Painel!C10="","",IF(AND(Painel!C10=0,Painel!B10&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D10="","",IF(Painel!D10&gt;=0," (+"," (")&amp;FIXED(Painel!D10*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E10&lt;&gt;"","; meta "&amp;IF(Indicadores!B10="R$","R$ ","")&amp;FIXED(Painel!E10,IF(Indicadores!C10="",0,Indicadores!C10))&amp;IF(OR(Indicadores!B10="R$",Indicadores!B10=""),""," "&amp;Indicadores!B10)&amp;", "&amp;LOWER(Painel!G10),"")&amp;".")</f>
         <v>• Taxa de conversão de leads: 4,4 % (-10% em relação a Agosto); meta 5,0 %, abaixo da meta.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="str">
-        <f>IF(OR(Indicadores!A11="",Painel!B11=""),"","• "&amp;Indicadores!A11&amp;": "&amp;IF(Indicadores!B11="R$","R$ ","")&amp;FIXED(Painel!B11,IF(Indicadores!C11="",0,Indicadores!C11))&amp;IF(OR(Indicadores!B11="R$",Indicadores!B11=""),""," "&amp;Indicadores!B11)&amp;IF(Painel!C11&lt;&gt;"",IF(Painel!D11&gt;=0," (+"," (")&amp;FIXED(Painel!D11*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E11&lt;&gt;"","; meta "&amp;IF(Indicadores!B11="R$","R$ ","")&amp;FIXED(Painel!E11,IF(Indicadores!C11="",0,Indicadores!C11))&amp;IF(OR(Indicadores!B11="R$",Indicadores!B11=""),""," "&amp;Indicadores!B11)&amp;", "&amp;LOWER(Painel!G11),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A11="",Painel!B11=""),"","• "&amp;Indicadores!A11&amp;": "&amp;IF(Indicadores!B11="R$","R$ ","")&amp;FIXED(Painel!B11,IF(Indicadores!C11="",0,Indicadores!C11))&amp;IF(OR(Indicadores!B11="R$",Indicadores!B11=""),""," "&amp;Indicadores!B11)&amp;IF(Painel!C11="","",IF(AND(Painel!C11=0,Painel!B11&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D11="","",IF(Painel!D11&gt;=0," (+"," (")&amp;FIXED(Painel!D11*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E11&lt;&gt;"","; meta "&amp;IF(Indicadores!B11="R$","R$ ","")&amp;FIXED(Painel!E11,IF(Indicadores!C11="",0,Indicadores!C11))&amp;IF(OR(Indicadores!B11="R$",Indicadores!B11=""),""," "&amp;Indicadores!B11)&amp;", "&amp;LOWER(Painel!G11),"")&amp;".")</f>
         <v>• Ticket médio: R$ 9.700 (+3% em relação a Agosto); meta R$ 9.000, no alvo.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="str">
-        <f>IF(OR(Indicadores!A12="",Painel!B12=""),"","• "&amp;Indicadores!A12&amp;": "&amp;IF(Indicadores!B12="R$","R$ ","")&amp;FIXED(Painel!B12,IF(Indicadores!C12="",0,Indicadores!C12))&amp;IF(OR(Indicadores!B12="R$",Indicadores!B12=""),""," "&amp;Indicadores!B12)&amp;IF(Painel!C12&lt;&gt;"",IF(Painel!D12&gt;=0," (+"," (")&amp;FIXED(Painel!D12*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E12&lt;&gt;"","; meta "&amp;IF(Indicadores!B12="R$","R$ ","")&amp;FIXED(Painel!E12,IF(Indicadores!C12="",0,Indicadores!C12))&amp;IF(OR(Indicadores!B12="R$",Indicadores!B12=""),""," "&amp;Indicadores!B12)&amp;", "&amp;LOWER(Painel!G12),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A12="",Painel!B12=""),"","• "&amp;Indicadores!A12&amp;": "&amp;IF(Indicadores!B12="R$","R$ ","")&amp;FIXED(Painel!B12,IF(Indicadores!C12="",0,Indicadores!C12))&amp;IF(OR(Indicadores!B12="R$",Indicadores!B12=""),""," "&amp;Indicadores!B12)&amp;IF(Painel!C12="","",IF(AND(Painel!C12=0,Painel!B12&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D12="","",IF(Painel!D12&gt;=0," (+"," (")&amp;FIXED(Painel!D12*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E12&lt;&gt;"","; meta "&amp;IF(Indicadores!B12="R$","R$ ","")&amp;FIXED(Painel!E12,IF(Indicadores!C12="",0,Indicadores!C12))&amp;IF(OR(Indicadores!B12="R$",Indicadores!B12=""),""," "&amp;Indicadores!B12)&amp;", "&amp;LOWER(Painel!G12),"")&amp;".")</f>
         <v>• Inadimplência: 2,4 % (-8% em relação a Agosto); meta 3,0 %, no alvo.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="19" t="str">
-        <f>IF(OR(Indicadores!A13="",Painel!B13=""),"","• "&amp;Indicadores!A13&amp;": "&amp;IF(Indicadores!B13="R$","R$ ","")&amp;FIXED(Painel!B13,IF(Indicadores!C13="",0,Indicadores!C13))&amp;IF(OR(Indicadores!B13="R$",Indicadores!B13=""),""," "&amp;Indicadores!B13)&amp;IF(Painel!C13&lt;&gt;"",IF(Painel!D13&gt;=0," (+"," (")&amp;FIXED(Painel!D13*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E13&lt;&gt;"","; meta "&amp;IF(Indicadores!B13="R$","R$ ","")&amp;FIXED(Painel!E13,IF(Indicadores!C13="",0,Indicadores!C13))&amp;IF(OR(Indicadores!B13="R$",Indicadores!B13=""),""," "&amp;Indicadores!B13)&amp;", "&amp;LOWER(Painel!G13),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A13="",Painel!B13=""),"","• "&amp;Indicadores!A13&amp;": "&amp;IF(Indicadores!B13="R$","R$ ","")&amp;FIXED(Painel!B13,IF(Indicadores!C13="",0,Indicadores!C13))&amp;IF(OR(Indicadores!B13="R$",Indicadores!B13=""),""," "&amp;Indicadores!B13)&amp;IF(Painel!C13="","",IF(AND(Painel!C13=0,Painel!B13&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D13="","",IF(Painel!D13&gt;=0," (+"," (")&amp;FIXED(Painel!D13*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E13&lt;&gt;"","; meta "&amp;IF(Indicadores!B13="R$","R$ ","")&amp;FIXED(Painel!E13,IF(Indicadores!C13="",0,Indicadores!C13))&amp;IF(OR(Indicadores!B13="R$",Indicadores!B13=""),""," "&amp;Indicadores!B13)&amp;", "&amp;LOWER(Painel!G13),"")&amp;".")</f>
         <v>• Atendimentos realizados: 63 un (-5% em relação a Agosto); meta 60 un, no alvo.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="str">
-        <f>IF(OR(Indicadores!A14="",Painel!B14=""),"","• "&amp;Indicadores!A14&amp;": "&amp;IF(Indicadores!B14="R$","R$ ","")&amp;FIXED(Painel!B14,IF(Indicadores!C14="",0,Indicadores!C14))&amp;IF(OR(Indicadores!B14="R$",Indicadores!B14=""),""," "&amp;Indicadores!B14)&amp;IF(Painel!C14&lt;&gt;"",IF(Painel!D14&gt;=0," (+"," (")&amp;FIXED(Painel!D14*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E14&lt;&gt;"","; meta "&amp;IF(Indicadores!B14="R$","R$ ","")&amp;FIXED(Painel!E14,IF(Indicadores!C14="",0,Indicadores!C14))&amp;IF(OR(Indicadores!B14="R$",Indicadores!B14=""),""," "&amp;Indicadores!B14)&amp;", "&amp;LOWER(Painel!G14),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A14="",Painel!B14=""),"","• "&amp;Indicadores!A14&amp;": "&amp;IF(Indicadores!B14="R$","R$ ","")&amp;FIXED(Painel!B14,IF(Indicadores!C14="",0,Indicadores!C14))&amp;IF(OR(Indicadores!B14="R$",Indicadores!B14=""),""," "&amp;Indicadores!B14)&amp;IF(Painel!C14="","",IF(AND(Painel!C14=0,Painel!B14&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D14="","",IF(Painel!D14&gt;=0," (+"," (")&amp;FIXED(Painel!D14*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E14&lt;&gt;"","; meta "&amp;IF(Indicadores!B14="R$","R$ ","")&amp;FIXED(Painel!E14,IF(Indicadores!C14="",0,Indicadores!C14))&amp;IF(OR(Indicadores!B14="R$",Indicadores!B14=""),""," "&amp;Indicadores!B14)&amp;", "&amp;LOWER(Painel!G14),"")&amp;".")</f>
         <v>• NPS: 72 pts (-1% em relação a Agosto); meta 70 pts, no alvo.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="str">
-        <f>IF(OR(Indicadores!A15="",Painel!B15=""),"","• "&amp;Indicadores!A15&amp;": "&amp;IF(Indicadores!B15="R$","R$ ","")&amp;FIXED(Painel!B15,IF(Indicadores!C15="",0,Indicadores!C15))&amp;IF(OR(Indicadores!B15="R$",Indicadores!B15=""),""," "&amp;Indicadores!B15)&amp;IF(Painel!C15&lt;&gt;"",IF(Painel!D15&gt;=0," (+"," (")&amp;FIXED(Painel!D15*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E15&lt;&gt;"","; meta "&amp;IF(Indicadores!B15="R$","R$ ","")&amp;FIXED(Painel!E15,IF(Indicadores!C15="",0,Indicadores!C15))&amp;IF(OR(Indicadores!B15="R$",Indicadores!B15=""),""," "&amp;Indicadores!B15)&amp;", "&amp;LOWER(Painel!G15),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A15="",Painel!B15=""),"","• "&amp;Indicadores!A15&amp;": "&amp;IF(Indicadores!B15="R$","R$ ","")&amp;FIXED(Painel!B15,IF(Indicadores!C15="",0,Indicadores!C15))&amp;IF(OR(Indicadores!B15="R$",Indicadores!B15=""),""," "&amp;Indicadores!B15)&amp;IF(Painel!C15="","",IF(AND(Painel!C15=0,Painel!B15&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D15="","",IF(Painel!D15&gt;=0," (+"," (")&amp;FIXED(Painel!D15*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E15&lt;&gt;"","; meta "&amp;IF(Indicadores!B15="R$","R$ ","")&amp;FIXED(Painel!E15,IF(Indicadores!C15="",0,Indicadores!C15))&amp;IF(OR(Indicadores!B15="R$",Indicadores!B15=""),""," "&amp;Indicadores!B15)&amp;", "&amp;LOWER(Painel!G15),"")&amp;".")</f>
         <v>• Horas extras da equipe: 12 h (-14% em relação a Agosto); meta 20 h, no alvo.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="str">
-        <f>IF(OR(Indicadores!A16="",Painel!B16=""),"","• "&amp;Indicadores!A16&amp;": "&amp;IF(Indicadores!B16="R$","R$ ","")&amp;FIXED(Painel!B16,IF(Indicadores!C16="",0,Indicadores!C16))&amp;IF(OR(Indicadores!B16="R$",Indicadores!B16=""),""," "&amp;Indicadores!B16)&amp;IF(Painel!C16&lt;&gt;"",IF(Painel!D16&gt;=0," (+"," (")&amp;FIXED(Painel!D16*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")","")&amp;IF(Painel!E16&lt;&gt;"","; meta "&amp;IF(Indicadores!B16="R$","R$ ","")&amp;FIXED(Painel!E16,IF(Indicadores!C16="",0,Indicadores!C16))&amp;IF(OR(Indicadores!B16="R$",Indicadores!B16=""),""," "&amp;Indicadores!B16)&amp;", "&amp;LOWER(Painel!G16),"")&amp;".")</f>
+        <f>IF(OR(Indicadores!A16="",Painel!B16=""),"","• "&amp;Indicadores!A16&amp;": "&amp;IF(Indicadores!B16="R$","R$ ","")&amp;FIXED(Painel!B16,IF(Indicadores!C16="",0,Indicadores!C16))&amp;IF(OR(Indicadores!B16="R$",Indicadores!B16=""),""," "&amp;Indicadores!B16)&amp;IF(Painel!C16="","",IF(AND(Painel!C16=0,Painel!B16&lt;&gt;0)," (sem base de comparação: "&amp;Config!$B$8&amp;" foi zero)",IF(Painel!D16="","",IF(Painel!D16&gt;=0," (+"," (")&amp;FIXED(Painel!D16*100,0)&amp;"% em relação a "&amp;Config!$B$8&amp;")")))&amp;IF(Painel!E16&lt;&gt;"","; meta "&amp;IF(Indicadores!B16="R$","R$ ","")&amp;FIXED(Painel!E16,IF(Indicadores!C16="",0,Indicadores!C16))&amp;IF(OR(Indicadores!B16="R$",Indicadores!B16=""),""," "&amp;Indicadores!B16)&amp;", "&amp;LOWER(Painel!G16),"")&amp;".")</f>
         <v>• Custo por lead: R$ 40,70 (+3% em relação a Agosto); meta R$ 45,00, no alvo.</v>
       </c>
     </row>
